--- a/summary.xlsx
+++ b/summary.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21094" windowHeight="9805"/>
+    <workbookView windowWidth="28800" windowHeight="14055"/>
   </bookViews>
   <sheets>
     <sheet name="result_summary" sheetId="1" r:id="rId1"/>
@@ -2080,12 +2080,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F175"/>
-  <sheetFormatPr defaultColWidth="9.72972972972973" defaultRowHeight="14.1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9.73333333333333" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="2" width="41" customWidth="1"/>
-    <col min="4" max="4" width="12.3513513513514" customWidth="1"/>
-    <col min="5" max="5" width="54.3513513513514" customWidth="1"/>
-    <col min="6" max="6" width="53.1171171171171" customWidth="1"/>
+    <col min="4" max="4" width="12.35" customWidth="1"/>
+    <col min="5" max="5" width="54.35" customWidth="1"/>
+    <col min="6" max="6" width="53.1166666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2110,7 +2110,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
@@ -2130,7 +2130,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>9</v>
@@ -2150,7 +2150,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>12</v>
@@ -2170,7 +2170,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>14</v>
@@ -2190,7 +2190,7 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>14</v>
@@ -2210,7 +2210,7 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>18</v>
@@ -2230,7 +2230,7 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>21</v>
@@ -2250,7 +2250,7 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>14</v>
@@ -2270,7 +2270,7 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>14</v>
@@ -2290,7 +2290,7 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>24</v>
@@ -2310,7 +2310,7 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>27</v>
@@ -2330,7 +2330,7 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>14</v>
@@ -2350,7 +2350,7 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>14</v>
@@ -2370,7 +2370,7 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>14</v>
@@ -2390,7 +2390,7 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>32</v>
@@ -2410,7 +2410,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>35</v>
@@ -2430,7 +2430,7 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>14</v>
@@ -2450,7 +2450,7 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>14</v>
@@ -2470,7 +2470,7 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>38</v>
@@ -2490,7 +2490,7 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>41</v>
@@ -2510,7 +2510,7 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>14</v>
@@ -2530,7 +2530,7 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>14</v>
@@ -2550,7 +2550,7 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="1">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>14</v>
@@ -2570,7 +2570,7 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>46</v>
@@ -2590,7 +2590,7 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>49</v>
@@ -2610,7 +2610,7 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="1">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>14</v>
@@ -2630,7 +2630,7 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>14</v>
@@ -2650,7 +2650,7 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>14</v>
@@ -2670,7 +2670,7 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>54</v>
@@ -2690,7 +2690,7 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="1">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>57</v>
@@ -2710,7 +2710,7 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>14</v>
@@ -2730,7 +2730,7 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="1">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>14</v>
@@ -2750,7 +2750,7 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>60</v>
@@ -2770,7 +2770,7 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="1">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>63</v>
@@ -2790,7 +2790,7 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="1">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>14</v>
@@ -2810,7 +2810,7 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="1">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>14</v>
@@ -2830,7 +2830,7 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="1">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>66</v>
@@ -2850,7 +2850,7 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>69</v>
@@ -2870,7 +2870,7 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>72</v>
@@ -2890,7 +2890,7 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>14</v>
@@ -2910,7 +2910,7 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>14</v>
@@ -2930,7 +2930,7 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>75</v>
@@ -2950,7 +2950,7 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="1">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>78</v>
@@ -2970,7 +2970,7 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="1">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>14</v>
@@ -2990,7 +2990,7 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="1">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>14</v>
@@ -3010,7 +3010,7 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>14</v>
@@ -3030,7 +3030,7 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="1">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>83</v>
@@ -3050,7 +3050,7 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>86</v>
@@ -3070,7 +3070,7 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>14</v>
@@ -3090,7 +3090,7 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="1">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>14</v>
@@ -3110,7 +3110,7 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>89</v>
@@ -3130,7 +3130,7 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>92</v>
@@ -3150,7 +3150,7 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="1">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>14</v>
@@ -3170,7 +3170,7 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>14</v>
@@ -3190,7 +3190,7 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="1">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>14</v>
@@ -3210,7 +3210,7 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="1">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>97</v>
@@ -3230,7 +3230,7 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="1">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>100</v>
@@ -3250,7 +3250,7 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="1">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>14</v>
@@ -3270,7 +3270,7 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="1">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>14</v>
@@ -3290,7 +3290,7 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="1">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>14</v>
@@ -3310,7 +3310,7 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="1">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>105</v>
@@ -3330,7 +3330,7 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="1">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>108</v>
@@ -3350,7 +3350,7 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="1">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>14</v>
@@ -3370,7 +3370,7 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="1">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>14</v>
@@ -3390,7 +3390,7 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="1">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>111</v>
@@ -3410,7 +3410,7 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="1">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>114</v>
@@ -3430,7 +3430,7 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>14</v>
@@ -3450,7 +3450,7 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="1">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>14</v>
@@ -3470,7 +3470,7 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="1">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>117</v>
@@ -3490,7 +3490,7 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="1">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>120</v>
@@ -3510,7 +3510,7 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="1">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>14</v>
@@ -3530,7 +3530,7 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="1">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>14</v>
@@ -3550,7 +3550,7 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="1">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>14</v>
@@ -3570,7 +3570,7 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="1">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>125</v>
@@ -3590,7 +3590,7 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="1">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>128</v>
@@ -3610,7 +3610,7 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="1">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>14</v>
@@ -3630,7 +3630,7 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="1">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>14</v>
@@ -3650,7 +3650,7 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="1">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>131</v>
@@ -3670,7 +3670,7 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="1">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>134</v>
@@ -3690,7 +3690,7 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="1">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>14</v>
@@ -3710,7 +3710,7 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="1">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>14</v>
@@ -3730,7 +3730,7 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="1">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>14</v>
@@ -3750,7 +3750,7 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="1">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>139</v>
@@ -3770,7 +3770,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="1">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>142</v>
@@ -3790,7 +3790,7 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="1">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>14</v>
@@ -3810,7 +3810,7 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="1">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>14</v>
@@ -3830,7 +3830,7 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="1">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>14</v>
@@ -3850,7 +3850,7 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="1">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>147</v>
@@ -3870,7 +3870,7 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="1">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>150</v>
@@ -3890,7 +3890,7 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="1">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>14</v>
@@ -3910,7 +3910,7 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="1">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>14</v>
@@ -3930,7 +3930,7 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="1">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>153</v>
@@ -3950,7 +3950,7 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="1">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>156</v>
@@ -3970,7 +3970,7 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="1">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>14</v>
@@ -3990,7 +3990,7 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="1">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>14</v>
@@ -4010,7 +4010,7 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="1">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>159</v>
@@ -4030,7 +4030,7 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="1">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>162</v>
@@ -4050,7 +4050,7 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="1">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>165</v>
@@ -4070,7 +4070,7 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="1">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>14</v>
@@ -4090,7 +4090,7 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="1">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>14</v>
@@ -4110,7 +4110,7 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="1">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>168</v>
@@ -4130,7 +4130,7 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="1">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>171</v>
@@ -4150,7 +4150,7 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="1">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>14</v>
@@ -4170,7 +4170,7 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="1">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>14</v>
@@ -4190,7 +4190,7 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="1">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>14</v>
@@ -4210,7 +4210,7 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="1">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>176</v>
@@ -4230,7 +4230,7 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="1">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>179</v>
@@ -4250,7 +4250,7 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="1">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>14</v>
@@ -4270,7 +4270,7 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="1">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>14</v>
@@ -4290,7 +4290,7 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="1">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>182</v>
@@ -4310,7 +4310,7 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="1">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>185</v>
@@ -4330,7 +4330,7 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="1">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>14</v>
@@ -4350,7 +4350,7 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="1">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>14</v>
@@ -4370,7 +4370,7 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="1">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>14</v>
@@ -4390,7 +4390,7 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="1">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>190</v>
@@ -4410,7 +4410,7 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="1">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>193</v>
@@ -4430,7 +4430,7 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="1">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>14</v>
@@ -4450,7 +4450,7 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="1">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>14</v>
@@ -4470,7 +4470,7 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="1">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>14</v>
@@ -4490,7 +4490,7 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="1">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>198</v>
@@ -4510,7 +4510,7 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="1">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>201</v>
@@ -4530,7 +4530,7 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="1">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>14</v>
@@ -4550,7 +4550,7 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="1">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>14</v>
@@ -4570,7 +4570,7 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="1">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>204</v>
@@ -4590,7 +4590,7 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="1">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>207</v>
@@ -4610,7 +4610,7 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="1">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>14</v>
@@ -4630,7 +4630,7 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="1">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>14</v>
@@ -4650,7 +4650,7 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="1">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>210</v>
@@ -4670,7 +4670,7 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="1">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>213</v>
@@ -4690,7 +4690,7 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="1">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>14</v>
@@ -4710,7 +4710,7 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="1">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>14</v>
@@ -4730,7 +4730,7 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="1">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>14</v>
@@ -4750,7 +4750,7 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="1">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>218</v>
@@ -4770,7 +4770,7 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="1">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>221</v>
@@ -4790,7 +4790,7 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="1">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>14</v>
@@ -4810,7 +4810,7 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="1">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>14</v>
@@ -4830,7 +4830,7 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="1">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>224</v>
@@ -4850,7 +4850,7 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="1">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>227</v>
@@ -4870,7 +4870,7 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="1">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>14</v>
@@ -4890,7 +4890,7 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="1">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>14</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="1">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>14</v>
@@ -4930,7 +4930,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="1">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>232</v>
@@ -4950,7 +4950,7 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="1">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>235</v>
@@ -4970,7 +4970,7 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="1">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>14</v>
@@ -4990,7 +4990,7 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="1">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>14</v>
@@ -5010,7 +5010,7 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="1">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>14</v>
@@ -5030,7 +5030,7 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="1">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>240</v>
@@ -5050,7 +5050,7 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="1">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>243</v>
@@ -5070,7 +5070,7 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="1">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>14</v>
@@ -5090,7 +5090,7 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="1">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>14</v>
@@ -5110,7 +5110,7 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="1">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>246</v>
@@ -5130,7 +5130,7 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="1">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>249</v>
@@ -5150,7 +5150,7 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="1">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>252</v>
@@ -5170,7 +5170,7 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="1">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>14</v>
@@ -5190,7 +5190,7 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" s="1">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>14</v>
@@ -5210,7 +5210,7 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" s="1">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>255</v>
@@ -5230,7 +5230,7 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" s="1">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>258</v>
@@ -5250,7 +5250,7 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="1">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>14</v>
@@ -5270,7 +5270,7 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" s="1">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>14</v>
@@ -5290,7 +5290,7 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="1">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>261</v>
@@ -5310,7 +5310,7 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" s="1">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>264</v>
@@ -5330,7 +5330,7 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="1">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>267</v>
@@ -5350,7 +5350,7 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" s="1">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>270</v>
@@ -5370,7 +5370,7 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="1">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>273</v>
@@ -5390,7 +5390,7 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" s="1">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>276</v>
@@ -5410,7 +5410,7 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="1">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>14</v>
@@ -5430,7 +5430,7 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" s="1">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>14</v>
@@ -5450,7 +5450,7 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="1">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>279</v>
@@ -5470,7 +5470,7 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" s="1">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>282</v>
@@ -5490,7 +5490,7 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="1">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>285</v>
@@ -5510,7 +5510,7 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" s="1">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>288</v>
@@ -5530,7 +5530,7 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="1">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>291</v>
@@ -5550,7 +5550,7 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="1">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>294</v>
@@ -5570,7 +5570,7 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="1">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>296</v>
